--- a/data/trans_orig/IP25B01_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25B01_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12080</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>12781</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57245</t>
+          <t>55194</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18441</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68245</t>
+          <t>69203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12674</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>29717</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23475</t>
+          <t>23494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35653</t>
+          <t>35126</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52324</t>
+          <t>51748</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29528</t>
+          <t>30357</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52938</t>
+          <t>53879</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69335</t>
+          <t>70631</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100129</t>
+          <t>98261</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44869</t>
+          <t>44378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61595</t>
+          <t>61884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37591</t>
+          <t>37221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62993</t>
+          <t>63715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85908</t>
+          <t>86449</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118159</t>
+          <t>117528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16123</t>
+          <t>15885</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>26052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37256</t>
+          <t>37548</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>21057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39142</t>
+          <t>38654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45225</t>
+          <t>47493</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50672</t>
+          <t>50521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79240</t>
+          <t>77276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57387</t>
+          <t>58637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81004</t>
+          <t>81525</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97290</t>
+          <t>97932</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128362</t>
+          <t>128334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165400</t>
+          <t>163101</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203259</t>
+          <t>203272</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69320</t>
+          <t>69493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96505</t>
+          <t>95623</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>75708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>104479</t>
+          <t>104520</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>151144</t>
+          <t>151673</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>191966</t>
+          <t>190223</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,92%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20059</t>
+          <t>19060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99543</t>
+          <t>102466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>35490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39477</t>
+          <t>37925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>146580</t>
+          <t>135878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>15231</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39423</t>
+          <t>38365</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22510</t>
+          <t>23135</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42376</t>
+          <t>42301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>40809</t>
+          <t>41082</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>74634</t>
+          <t>74658</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40673</t>
+          <t>40932</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83343</t>
+          <t>82972</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57073</t>
+          <t>55985</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84943</t>
+          <t>84331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104232</t>
+          <t>105969</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159293</t>
+          <t>159022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28500</t>
+          <t>30225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60790</t>
+          <t>61804</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46310</t>
+          <t>46314</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70084</t>
+          <t>69865</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>79877</t>
+          <t>81591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123253</t>
+          <t>125329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7017</t>
+          <t>6475</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19775</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13065</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29041</t>
+          <t>28320</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>32740</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13653</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>29369</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34189</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56181</t>
+          <t>56982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59929</t>
+          <t>58813</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81393</t>
+          <t>80529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>55733</t>
+          <t>58125</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80453</t>
+          <t>81099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>122907</t>
+          <t>123107</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>154050</t>
+          <t>153835</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51120</t>
+          <t>50258</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72755</t>
+          <t>71154</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67549</t>
+          <t>67756</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90874</t>
+          <t>90818</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>126237</t>
+          <t>124522</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>157149</t>
+          <t>154427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40257</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>152464</t>
+          <t>160064</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>57571</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>113910</t>
+          <t>115881</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>108760</t>
+          <t>111108</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>234273</t>
+          <t>238409</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74195</t>
+          <t>72606</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>112022</t>
+          <t>109903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>88325</t>
+          <t>87914</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123518</t>
+          <t>124397</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>171508</t>
+          <t>175662</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>224686</t>
+          <t>227935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>212103</t>
+          <t>214427</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>271225</t>
+          <t>274063</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>267664</t>
+          <t>268184</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>320955</t>
+          <t>321684</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>500908</t>
+          <t>500241</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>580998</t>
+          <t>578389</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>209396</t>
+          <t>208013</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>267429</t>
+          <t>266894</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>251124</t>
+          <t>251236</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>300815</t>
+          <t>303049</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>476781</t>
+          <t>474665</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>554660</t>
+          <t>559719</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25B01_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25B01_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de horas al día que emplean en utilizar aparatos electrónicos entre semana / solo 2023 en 2023 (tasa de respuesta: 98,33%)</t>
+          <t>Menores según el número de horas al día que utilizan aparatos electrónicos entre semana en 2023 (tasa de respuesta: 98,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20257</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9784</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>43054</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,09%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6449</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3314</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11552</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27935</t>
+          <t>6722</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55194</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34384</t>
+          <t>26979</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69203</t>
+          <t>52207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18744</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11853</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27410</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>21,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12314</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7282</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19405</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,74%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29717</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>32434</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23494</t>
+          <t>23020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43217</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,95%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>41813</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31759</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>52814</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>33,21%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>25,22%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>41,95%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>43009</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>35126</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>51748</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>37,53%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,65%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>45,15%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41994</t>
+          <t>45961</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30357</t>
+          <t>37738</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>53879</t>
+          <t>55638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>87774</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70631</t>
+          <t>72614</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98261</t>
+          <t>101204</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>45092</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33509</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56561</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,81%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>52830</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>44378</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>61884</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46,1%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>38,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>54,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50366</t>
+          <t>51920</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37221</t>
+          <t>43088</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63715</t>
+          <t>60567</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>103196</t>
+          <t>97012</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86449</t>
+          <t>80539</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117528</t>
+          <t>110730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,34%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>114602</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>114602</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>114602</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>118293</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>118293</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>118293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>255014</t>
+          <t>244199</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>255014</t>
+          <t>244199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>255014</t>
+          <t>244199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>15889</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9509</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>26253</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9339</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5244</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>15885</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26052</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>25813</t>
+          <t>25406</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37548</t>
+          <t>36983</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31735</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23284</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>42594</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>29129</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>21057</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38654</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,42%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34240</t>
+          <t>30423</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>22105</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47493</t>
+          <t>40367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>63369</t>
+          <t>62159</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50521</t>
+          <t>50368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77276</t>
+          <t>76912</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>109988</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>95498</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>124973</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>40,42%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>52,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>69732</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58637</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>81525</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>36,83%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>113394</t>
+          <t>71116</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97932</t>
+          <t>59820</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128334</t>
+          <t>83213</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>183126</t>
+          <t>181105</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163101</t>
+          <t>163780</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203272</t>
+          <t>199811</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>78646</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>66464</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>92480</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>28,13%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>39,14%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>81134</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>69493</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>95623</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>42,85%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>36,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>50,5%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>89788</t>
+          <t>72321</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75708</t>
+          <t>60764</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>104520</t>
+          <t>82958</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>170922</t>
+          <t>150966</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>151673</t>
+          <t>134239</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>190223</t>
+          <t>167345</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>236258</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>236258</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>236258</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>189334</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>189334</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>189334</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>253896</t>
+          <t>183377</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>253896</t>
+          <t>183377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>253896</t>
+          <t>183377</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>443230</t>
+          <t>419635</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>443230</t>
+          <t>419635</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>443230</t>
+          <t>419635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21057</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12815</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34086</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>45572</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19060</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>102466</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>24,75%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>55,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21436</t>
+          <t>22044</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35490</t>
+          <t>31973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>67008</t>
+          <t>43101</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>31321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135878</t>
+          <t>57370</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30628</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>21645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>40766</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>24,89%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>25617</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>15231</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>38365</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>13,91%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31595</t>
+          <t>21569</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23135</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42301</t>
+          <t>30006</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>57212</t>
+          <t>52197</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>41082</t>
+          <t>40976</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>74658</t>
+          <t>65549</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>61327</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>50563</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>73908</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>37,45%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>45,13%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>65375</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>40932</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>82972</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>35,5%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>70087</t>
+          <t>60272</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55985</t>
+          <t>50393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84331</t>
+          <t>70509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>135462</t>
+          <t>121600</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105969</t>
+          <t>105421</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159022</t>
+          <t>138519</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,99%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>50752</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>40311</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>60283</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,62%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>36,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>47583</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>30225</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>61804</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>25,84%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,41%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>33,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>57559</t>
+          <t>47224</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46314</t>
+          <t>37513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69865</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>105142</t>
+          <t>97976</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81591</t>
+          <t>85046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>125329</t>
+          <t>114062</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>163765</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>163765</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>163765</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>184147</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>184147</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>184147</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>180677</t>
+          <t>151109</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>180677</t>
+          <t>151109</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>180677</t>
+          <t>151109</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>364824</t>
+          <t>314874</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>364824</t>
+          <t>314874</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>364824</t>
+          <t>314874</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>11588</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6693</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>18962</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>11,27%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>7331</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>3936</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>13271</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>8,15%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>19280</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13191</t>
+          <t>13304</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28320</t>
+          <t>29747</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>18580</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>12308</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>26088</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>24781</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>17037</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>32740</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>15,21%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>20,1%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20066</t>
+          <t>25507</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13840</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29369</t>
+          <t>35071</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>44847</t>
+          <t>44087</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>34758</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56982</t>
+          <t>55786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>63011</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>52910</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>73927</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>37,45%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>31,45%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>43,94%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>69849</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>58813</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>80529</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>42,88%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>36,1%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>49,43%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68355</t>
+          <t>71345</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58125</t>
+          <t>60576</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>81099</t>
+          <t>82381</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>138204</t>
+          <t>134356</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>123107</t>
+          <t>118538</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>153835</t>
+          <t>150093</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>75082</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>63807</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>85719</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>44,62%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>37,92%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>50,94%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>60950</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>50258</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>71154</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>37,41%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>30,85%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>43,68%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>79637</t>
+          <t>57805</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67756</t>
+          <t>48477</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90818</t>
+          <t>68641</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>140587</t>
+          <t>132887</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124522</t>
+          <t>118897</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>154427</t>
+          <t>150485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>168261</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>168261</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>168261</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>162912</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>162912</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>162912</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>180075</t>
+          <t>162350</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>180075</t>
+          <t>162350</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>180075</t>
+          <t>162350</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>342986</t>
+          <t>330611</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>342986</t>
+          <t>330611</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>342986</t>
+          <t>330611</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>68791</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>51871</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>100354</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>14,46%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>68690</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>40413</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>160064</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>24,59%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>77863</t>
+          <t>45975</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57571</t>
+          <t>34911</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>115881</t>
+          <t>59058</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>146553</t>
+          <t>114766</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>111108</t>
+          <t>95411</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>238409</t>
+          <t>148465</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>99687</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>83914</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>118822</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>14,36%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>17,12%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>91842</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>72606</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>109903</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>16,88%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>106017</t>
+          <t>91190</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87914</t>
+          <t>75460</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>124397</t>
+          <t>107556</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>197859</t>
+          <t>190877</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>175662</t>
+          <t>167559</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>227935</t>
+          <t>215588</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>276140</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>250839</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>300646</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>39,78%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>366</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>247965</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>214427</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>274063</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>38,09%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>42,1%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>293829</t>
+          <t>248695</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>268184</t>
+          <t>227158</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>321684</t>
+          <t>266924</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>541795</t>
+          <t>524834</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>500241</t>
+          <t>491685</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>578389</t>
+          <t>556119</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>249572</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>225149</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>272680</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>32,43%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>39,28%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>371</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>242497</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>208013</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>266894</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>37,25%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>31,95%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>41,0%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>277350</t>
+          <t>229270</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>251236</t>
+          <t>211344</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>303049</t>
+          <t>251830</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>519847</t>
+          <t>478842</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>474665</t>
+          <t>446733</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>559719</t>
+          <t>508862</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>38,86%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>694190</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>694190</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>694190</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>919</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>650994</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>650994</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>650994</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>755060</t>
+          <t>615130</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>755060</t>
+          <t>615130</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>755060</t>
+          <t>615130</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1406055</t>
+          <t>1309319</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1406055</t>
+          <t>1309319</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1406055</t>
+          <t>1309319</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
